--- a/Documentos/Documentos Excel - Hojas de calculo/Filtrar.xlsx
+++ b/Documentos/Documentos Excel - Hojas de calculo/Filtrar.xlsx
@@ -107,10 +107,10 @@
     <t>Filtrar los alumnos cuya Nota sea mayor a 5 Y menor a 9.</t>
   </si>
   <si>
-    <t>Filtrar los alumnos cuya Edad sea mayor a 15 O cuyo Estado sea 'Desaprobado'.</t>
-  </si>
-  <si>
     <t>Filtrar los alumnos cuyo Curso sea '5°A' Y cuya Nota sea mayor a 5.</t>
+  </si>
+  <si>
+    <t>Filtrar los alumnos cuya Edad sea mayor a 15 Y cuyo Estado sea 'Desaprobado'.</t>
   </si>
 </sst>
 </file>
@@ -599,7 +599,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1599,7 +1599,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
